--- a/myapp/ClaendarioHORASfct.xlsx
+++ b/myapp/ClaendarioHORASfct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\App_TecnoMat\app_lectorArchivos\myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C894A62D-3803-4CEC-BDA2-0547CA5ED055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E55ECD2-2730-4F0B-A5E6-49A75B587410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="2475" windowWidth="21600" windowHeight="11385" xr2:uid="{0FF1313B-63B8-4083-9BFB-EA45AC4F463B}"/>
+    <workbookView xWindow="4785" yWindow="2820" windowWidth="21600" windowHeight="11385" xr2:uid="{0FF1313B-63B8-4083-9BFB-EA45AC4F463B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Calendario FCT 2026</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>11 - 17 may 2026</t>
+  </si>
+  <si>
+    <t>18 - 24 may 2026</t>
   </si>
 </sst>
 </file>
@@ -270,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -309,6 +312,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,23 +679,23 @@
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4">
-        <v>8</v>
-      </c>
-      <c r="E3" s="4">
-        <v>8</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="B3" s="14">
+        <v>8</v>
+      </c>
+      <c r="C3" s="14">
+        <v>8</v>
+      </c>
+      <c r="D3" s="14">
+        <v>8</v>
+      </c>
+      <c r="E3" s="14">
+        <v>8</v>
+      </c>
+      <c r="F3" s="14">
         <v>8</v>
       </c>
       <c r="G3" s="2">
-        <f>SUM(B3:F3)</f>
+        <f t="shared" ref="G3:G14" si="0">SUM(B3:F3)</f>
         <v>40</v>
       </c>
     </row>
@@ -697,23 +703,23 @@
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="B4" s="14">
+        <v>8</v>
+      </c>
+      <c r="C4" s="14">
+        <v>8</v>
+      </c>
+      <c r="D4" s="14">
+        <v>8</v>
+      </c>
+      <c r="E4" s="14">
         <v>0</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="14">
         <v>8</v>
       </c>
       <c r="G4" s="11">
-        <f>SUM(B4:F4)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -721,23 +727,23 @@
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="4">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="B5" s="14">
+        <v>8</v>
+      </c>
+      <c r="C5" s="14">
+        <v>8</v>
+      </c>
+      <c r="D5" s="14">
+        <v>8</v>
+      </c>
+      <c r="E5" s="14">
         <v>0</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="14">
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <f>SUM(B5:F5)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
@@ -745,23 +751,23 @@
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="B6" s="14">
+        <v>8</v>
+      </c>
+      <c r="C6" s="14">
+        <v>8</v>
+      </c>
+      <c r="D6" s="14">
+        <v>8</v>
+      </c>
+      <c r="E6" s="14">
+        <v>8</v>
+      </c>
+      <c r="F6" s="14">
         <v>8</v>
       </c>
       <c r="G6" s="2">
-        <f>SUM(B6:F6)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
@@ -769,23 +775,23 @@
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="B7" s="14">
+        <v>8</v>
+      </c>
+      <c r="C7" s="14">
+        <v>8</v>
+      </c>
+      <c r="D7" s="14">
+        <v>8</v>
+      </c>
+      <c r="E7" s="14">
+        <v>8</v>
+      </c>
+      <c r="F7" s="14">
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <f>SUM(B7:F7)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -793,23 +799,23 @@
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="14">
         <v>0</v>
       </c>
-      <c r="C8" s="4">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4">
-        <v>8</v>
-      </c>
-      <c r="E8" s="4">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="C8" s="14">
+        <v>8</v>
+      </c>
+      <c r="D8" s="14">
+        <v>8</v>
+      </c>
+      <c r="E8" s="14">
+        <v>8</v>
+      </c>
+      <c r="F8" s="14">
         <v>8</v>
       </c>
       <c r="G8" s="2">
-        <f>SUM(B8:F8)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -817,23 +823,23 @@
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="14">
         <v>0</v>
       </c>
-      <c r="C9" s="4">
-        <v>8</v>
-      </c>
-      <c r="D9" s="4">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="C9" s="14">
+        <v>8</v>
+      </c>
+      <c r="D9" s="14">
+        <v>8</v>
+      </c>
+      <c r="E9" s="14">
+        <v>8</v>
+      </c>
+      <c r="F9" s="14">
         <v>8</v>
       </c>
       <c r="G9" s="2">
-        <f>SUM(B9:F9)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -841,23 +847,23 @@
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="4">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4">
-        <v>8</v>
-      </c>
-      <c r="E10" s="4">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="B10" s="14">
+        <v>8</v>
+      </c>
+      <c r="C10" s="14">
+        <v>8</v>
+      </c>
+      <c r="D10" s="14">
+        <v>8</v>
+      </c>
+      <c r="E10" s="14">
+        <v>8</v>
+      </c>
+      <c r="F10" s="14">
         <v>8</v>
       </c>
       <c r="G10" s="2">
-        <f>SUM(B10:F10)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
@@ -865,23 +871,23 @@
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4">
-        <v>8</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="B11" s="14">
+        <v>8</v>
+      </c>
+      <c r="C11" s="14">
+        <v>8</v>
+      </c>
+      <c r="D11" s="14">
+        <v>8</v>
+      </c>
+      <c r="E11" s="14">
+        <v>8</v>
+      </c>
+      <c r="F11" s="14">
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <f>SUM(B11:F11)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -889,23 +895,23 @@
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="4">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4">
-        <v>8</v>
-      </c>
-      <c r="E12" s="4">
-        <v>8</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="B12" s="14">
+        <v>8</v>
+      </c>
+      <c r="C12" s="14">
+        <v>8</v>
+      </c>
+      <c r="D12" s="14">
+        <v>8</v>
+      </c>
+      <c r="E12" s="14">
+        <v>8</v>
+      </c>
+      <c r="F12" s="14">
         <v>8</v>
       </c>
       <c r="G12" s="2">
-        <f>SUM(B12:F12)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
@@ -913,47 +919,47 @@
       <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="4">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4">
-        <v>8</v>
-      </c>
-      <c r="E13" s="4">
-        <v>8</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="B13" s="14">
+        <v>8</v>
+      </c>
+      <c r="C13" s="14">
+        <v>8</v>
+      </c>
+      <c r="D13" s="14">
+        <v>8</v>
+      </c>
+      <c r="E13" s="14">
+        <v>8</v>
+      </c>
+      <c r="F13" s="14">
         <v>8</v>
       </c>
       <c r="G13" s="2">
-        <f>SUM(B13:F13)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4">
-        <v>8</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="14">
+        <v>8</v>
+      </c>
+      <c r="C14" s="14">
+        <v>8</v>
+      </c>
+      <c r="D14" s="14">
         <v>0</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="14">
         <v>0</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="14">
         <v>0</v>
       </c>
       <c r="G14" s="2">
-        <f>SUM(B14:F14)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
